--- a/res/efficiency/pet-md/ollama-solar-pro-preview-instruct-Q4_K_S/2025-02-12_12-10-47/stats_by_iteration-solar-pro-preview-instruct-Q4_K_S.xlsx
+++ b/res/efficiency/pet-md/ollama-solar-pro-preview-instruct-Q4_K_S/2025-02-12_12-10-47/stats_by_iteration-solar-pro-preview-instruct-Q4_K_S.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>P</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>avg. power draw</t>
+  </si>
+  <si>
+    <t>output tokens</t>
+  </si>
+  <si>
+    <t>throughput</t>
   </si>
   <si>
     <t>parse_err</t>
@@ -494,10 +500,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -510,8 +516,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0.118735</v>
       </c>
@@ -524,8 +536,14 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>34418</v>
+      </c>
+      <c r="F2">
+        <v>23.72019297036526</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>0.131768</v>
       </c>
@@ -538,8 +556,14 @@
       <c r="D3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>40911</v>
+      </c>
+      <c r="F3">
+        <v>25.41055900621118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>0.14356</v>
       </c>
@@ -552,8 +576,14 @@
       <c r="D4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>46172</v>
+      </c>
+      <c r="F4">
+        <v>26.33884768967484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>0.128009</v>
       </c>
@@ -566,8 +596,14 @@
       <c r="D5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>39744</v>
+      </c>
+      <c r="F5">
+        <v>25.37931034482759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>0.128431</v>
       </c>
@@ -579,6 +615,12 @@
       </c>
       <c r="D6">
         <v>5</v>
+      </c>
+      <c r="E6">
+        <v>39597</v>
+      </c>
+      <c r="F6">
+        <v>25.23709369024857</v>
       </c>
     </row>
   </sheetData>
@@ -593,10 +635,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2">
